--- a/akbar_report.xlsx
+++ b/akbar_report.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sunday, 14 June 2026, 03:19 AM</t>
+          <t>Sunday, 14 June 2026, 03:26 AM</t>
         </is>
       </c>
     </row>
@@ -791,25 +791,48 @@
       </c>
       <c r="E16" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>400.00</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>TOTAL SPENDING</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>RM 1020.00</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>RM 1420.00</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/akbar_report.xlsx
+++ b/akbar_report.xlsx
@@ -45,7 +45,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,16 +60,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002563EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -111,23 +101,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,7 +508,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sunday, 14 June 2026, 03:26 AM</t>
+          <t>Monday, 15 June 2026, 09:12 PM</t>
         </is>
       </c>
     </row>
@@ -561,277 +539,24 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
+          <t>TOTAL SPENDING</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Bills</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>400.00</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL SPENDING</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>RM 1420.00</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="n"/>
+          <t>RM 0.00</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/akbar_report.xlsx
+++ b/akbar_report.xlsx
@@ -45,7 +45,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +60,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -101,11 +111,23 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,7 +530,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Monday, 15 June 2026, 09:12 PM</t>
+          <t>Monday, 15 June 2026, 11:23 PM</t>
         </is>
       </c>
     </row>
@@ -539,25 +561,255 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>300.00</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
           <t>TOTAL SPENDING</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>RM 0.00</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>RM 1200.00</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/akbar_report.xlsx
+++ b/akbar_report.xlsx
@@ -45,7 +45,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,16 +60,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002563EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -111,23 +101,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,7 +508,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Monday, 15 June 2026, 11:23 PM</t>
+          <t>Monday, 15 June 2026, 09:58 PM</t>
         </is>
       </c>
     </row>
@@ -561,255 +539,25 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>300.00</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
+          <t>TOTAL SPENDING</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Bills</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL SPENDING</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>RM 1200.00</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="n"/>
+          <t>RM 0.00</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
